--- a/microcoach/Data/Classroom1/Session1/PPQ-StudentData.xlsx
+++ b/microcoach/Data/Classroom1/Session1/PPQ-StudentData.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:O68"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -485,6 +485,24 @@
       <c r="I3" t="str">
         <v>Q6</v>
       </c>
+      <c r="J3" t="str">
+        <v>Q1_Conf</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Q2_Conf</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Q3_Conf</v>
+      </c>
+      <c r="M3" t="str">
+        <v>Q4_Conf</v>
+      </c>
+      <c r="N3" t="str">
+        <v>Q5_Conf</v>
+      </c>
+      <c r="O3" t="str">
+        <v>Q6_Conf</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -514,6 +532,24 @@
       <c r="I4">
         <v>0.25</v>
       </c>
+      <c r="J4">
+        <v>3.73</v>
+      </c>
+      <c r="K4">
+        <v>3.4</v>
+      </c>
+      <c r="L4">
+        <v>3.4</v>
+      </c>
+      <c r="M4">
+        <v>3.32</v>
+      </c>
+      <c r="N4">
+        <v>3.37</v>
+      </c>
+      <c r="O4">
+        <v>3.05</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -659,6 +695,24 @@
       <c r="I9" t="str">
         <v>A</v>
       </c>
+      <c r="J9">
+        <v>5</v>
+      </c>
+      <c r="K9">
+        <v>4</v>
+      </c>
+      <c r="L9">
+        <v>5</v>
+      </c>
+      <c r="M9">
+        <v>4</v>
+      </c>
+      <c r="N9">
+        <v>4</v>
+      </c>
+      <c r="O9">
+        <v>5</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -688,6 +742,24 @@
       <c r="I10" t="str">
         <v>A</v>
       </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>2</v>
+      </c>
+      <c r="O10">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -717,6 +789,24 @@
       <c r="I11" t="str">
         <v>C</v>
       </c>
+      <c r="J11">
+        <v>5</v>
+      </c>
+      <c r="K11">
+        <v>5</v>
+      </c>
+      <c r="L11">
+        <v>5</v>
+      </c>
+      <c r="M11">
+        <v>5</v>
+      </c>
+      <c r="N11">
+        <v>5</v>
+      </c>
+      <c r="O11">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -746,6 +836,24 @@
       <c r="I12" t="str">
         <v>C</v>
       </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>2</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>2</v>
+      </c>
+      <c r="N12">
+        <v>2</v>
+      </c>
+      <c r="O12">
+        <v>2</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -775,6 +883,24 @@
       <c r="I13" t="str">
         <v>A</v>
       </c>
+      <c r="J13">
+        <v>3</v>
+      </c>
+      <c r="K13">
+        <v>4</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+      <c r="M13">
+        <v>2</v>
+      </c>
+      <c r="N13">
+        <v>4</v>
+      </c>
+      <c r="O13">
+        <v>5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -804,6 +930,24 @@
       <c r="I14" t="str">
         <v>B</v>
       </c>
+      <c r="J14">
+        <v>2</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>4</v>
+      </c>
+      <c r="M14">
+        <v>2</v>
+      </c>
+      <c r="N14">
+        <v>1</v>
+      </c>
+      <c r="O14">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -833,6 +977,24 @@
       <c r="I15" t="str">
         <v>C</v>
       </c>
+      <c r="J15">
+        <v>5</v>
+      </c>
+      <c r="K15">
+        <v>2</v>
+      </c>
+      <c r="L15">
+        <v>3</v>
+      </c>
+      <c r="M15">
+        <v>5</v>
+      </c>
+      <c r="N15">
+        <v>5</v>
+      </c>
+      <c r="O15">
+        <v>3</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -862,6 +1024,24 @@
       <c r="I16" t="str">
         <v>B</v>
       </c>
+      <c r="J16">
+        <v>4</v>
+      </c>
+      <c r="K16">
+        <v>3</v>
+      </c>
+      <c r="L16">
+        <v>4</v>
+      </c>
+      <c r="M16">
+        <v>1</v>
+      </c>
+      <c r="N16">
+        <v>4</v>
+      </c>
+      <c r="O16">
+        <v>3</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -891,6 +1071,24 @@
       <c r="I17" t="str">
         <v>A</v>
       </c>
+      <c r="J17">
+        <v>5</v>
+      </c>
+      <c r="K17">
+        <v>4</v>
+      </c>
+      <c r="L17">
+        <v>2</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="N17">
+        <v>2</v>
+      </c>
+      <c r="O17">
+        <v>5</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
@@ -920,6 +1118,24 @@
       <c r="I18" t="str">
         <v>B</v>
       </c>
+      <c r="J18">
+        <v>3</v>
+      </c>
+      <c r="K18">
+        <v>2</v>
+      </c>
+      <c r="L18">
+        <v>2</v>
+      </c>
+      <c r="M18">
+        <v>4</v>
+      </c>
+      <c r="N18">
+        <v>5</v>
+      </c>
+      <c r="O18">
+        <v>2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -949,6 +1165,24 @@
       <c r="I19" t="str">
         <v>B</v>
       </c>
+      <c r="J19">
+        <v>5</v>
+      </c>
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="L19">
+        <v>3</v>
+      </c>
+      <c r="M19">
+        <v>3</v>
+      </c>
+      <c r="N19">
+        <v>2</v>
+      </c>
+      <c r="O19">
+        <v>5</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -978,6 +1212,24 @@
       <c r="I20" t="str">
         <v>A</v>
       </c>
+      <c r="J20">
+        <v>3</v>
+      </c>
+      <c r="K20">
+        <v>5</v>
+      </c>
+      <c r="L20">
+        <v>1</v>
+      </c>
+      <c r="M20">
+        <v>4</v>
+      </c>
+      <c r="N20">
+        <v>1</v>
+      </c>
+      <c r="O20">
+        <v>4</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
@@ -1007,6 +1259,24 @@
       <c r="I21" t="str">
         <v>A</v>
       </c>
+      <c r="J21">
+        <v>5</v>
+      </c>
+      <c r="K21">
+        <v>3</v>
+      </c>
+      <c r="L21">
+        <v>3</v>
+      </c>
+      <c r="M21">
+        <v>3</v>
+      </c>
+      <c r="N21">
+        <v>3</v>
+      </c>
+      <c r="O21">
+        <v>2</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
@@ -1036,6 +1306,24 @@
       <c r="I22" t="str">
         <v>C</v>
       </c>
+      <c r="J22">
+        <v>5</v>
+      </c>
+      <c r="K22">
+        <v>5</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
+      </c>
+      <c r="M22">
+        <v>3</v>
+      </c>
+      <c r="N22">
+        <v>4</v>
+      </c>
+      <c r="O22">
+        <v>4</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
@@ -1065,6 +1353,24 @@
       <c r="I23" t="str">
         <v>B</v>
       </c>
+      <c r="J23">
+        <v>5</v>
+      </c>
+      <c r="K23">
+        <v>3</v>
+      </c>
+      <c r="L23">
+        <v>4</v>
+      </c>
+      <c r="M23">
+        <v>3</v>
+      </c>
+      <c r="N23">
+        <v>3</v>
+      </c>
+      <c r="O23">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
@@ -1094,6 +1400,24 @@
       <c r="I24" t="str">
         <v>A</v>
       </c>
+      <c r="J24">
+        <v>4</v>
+      </c>
+      <c r="K24">
+        <v>3</v>
+      </c>
+      <c r="L24">
+        <v>4</v>
+      </c>
+      <c r="M24">
+        <v>5</v>
+      </c>
+      <c r="N24">
+        <v>4</v>
+      </c>
+      <c r="O24">
+        <v>2</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
@@ -1123,6 +1447,24 @@
       <c r="I25" t="str">
         <v>C</v>
       </c>
+      <c r="J25">
+        <v>4</v>
+      </c>
+      <c r="K25">
+        <v>3</v>
+      </c>
+      <c r="L25">
+        <v>4</v>
+      </c>
+      <c r="M25">
+        <v>3</v>
+      </c>
+      <c r="N25">
+        <v>2</v>
+      </c>
+      <c r="O25">
+        <v>3</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
@@ -1152,6 +1494,24 @@
       <c r="I26" t="str">
         <v>B</v>
       </c>
+      <c r="J26">
+        <v>4</v>
+      </c>
+      <c r="K26">
+        <v>5</v>
+      </c>
+      <c r="L26">
+        <v>5</v>
+      </c>
+      <c r="M26">
+        <v>1</v>
+      </c>
+      <c r="N26">
+        <v>3</v>
+      </c>
+      <c r="O26">
+        <v>3</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -1181,6 +1541,24 @@
       <c r="I27" t="str">
         <v>B</v>
       </c>
+      <c r="J27">
+        <v>5</v>
+      </c>
+      <c r="K27">
+        <v>1</v>
+      </c>
+      <c r="L27">
+        <v>3</v>
+      </c>
+      <c r="M27">
+        <v>1</v>
+      </c>
+      <c r="N27">
+        <v>3</v>
+      </c>
+      <c r="O27">
+        <v>2</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
@@ -1210,6 +1588,24 @@
       <c r="I28" t="str">
         <v>A</v>
       </c>
+      <c r="J28">
+        <v>3</v>
+      </c>
+      <c r="K28">
+        <v>4</v>
+      </c>
+      <c r="L28">
+        <v>1</v>
+      </c>
+      <c r="M28">
+        <v>3</v>
+      </c>
+      <c r="N28">
+        <v>5</v>
+      </c>
+      <c r="O28">
+        <v>3</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
@@ -1239,6 +1635,24 @@
       <c r="I29" t="str">
         <v>B</v>
       </c>
+      <c r="J29">
+        <v>5</v>
+      </c>
+      <c r="K29">
+        <v>2</v>
+      </c>
+      <c r="L29">
+        <v>4</v>
+      </c>
+      <c r="M29">
+        <v>4</v>
+      </c>
+      <c r="N29">
+        <v>4</v>
+      </c>
+      <c r="O29">
+        <v>5</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
@@ -1268,6 +1682,24 @@
       <c r="I30" t="str">
         <v>C</v>
       </c>
+      <c r="J30">
+        <v>4</v>
+      </c>
+      <c r="K30">
+        <v>4</v>
+      </c>
+      <c r="L30">
+        <v>3</v>
+      </c>
+      <c r="M30">
+        <v>5</v>
+      </c>
+      <c r="N30">
+        <v>3</v>
+      </c>
+      <c r="O30">
+        <v>4</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
@@ -1297,6 +1729,24 @@
       <c r="I31" t="str">
         <v>B</v>
       </c>
+      <c r="J31">
+        <v>3</v>
+      </c>
+      <c r="K31">
+        <v>2</v>
+      </c>
+      <c r="L31">
+        <v>5</v>
+      </c>
+      <c r="M31">
+        <v>4</v>
+      </c>
+      <c r="N31">
+        <v>1</v>
+      </c>
+      <c r="O31">
+        <v>5</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
@@ -1326,6 +1776,24 @@
       <c r="I32" t="str">
         <v>D</v>
       </c>
+      <c r="J32">
+        <v>5</v>
+      </c>
+      <c r="K32">
+        <v>2</v>
+      </c>
+      <c r="L32">
+        <v>3</v>
+      </c>
+      <c r="M32">
+        <v>1</v>
+      </c>
+      <c r="N32">
+        <v>2</v>
+      </c>
+      <c r="O32">
+        <v>2</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
@@ -1355,6 +1823,24 @@
       <c r="I33" t="str">
         <v>B</v>
       </c>
+      <c r="J33">
+        <v>4</v>
+      </c>
+      <c r="K33">
+        <v>2</v>
+      </c>
+      <c r="L33">
+        <v>2</v>
+      </c>
+      <c r="M33">
+        <v>3</v>
+      </c>
+      <c r="N33">
+        <v>2</v>
+      </c>
+      <c r="O33">
+        <v>1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
@@ -1384,6 +1870,24 @@
       <c r="I34" t="str">
         <v>C</v>
       </c>
+      <c r="J34">
+        <v>5</v>
+      </c>
+      <c r="K34">
+        <v>5</v>
+      </c>
+      <c r="L34">
+        <v>3</v>
+      </c>
+      <c r="M34">
+        <v>3</v>
+      </c>
+      <c r="N34">
+        <v>3</v>
+      </c>
+      <c r="O34">
+        <v>4</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
@@ -1413,6 +1917,24 @@
       <c r="I35" t="str">
         <v>A</v>
       </c>
+      <c r="J35">
+        <v>4</v>
+      </c>
+      <c r="K35">
+        <v>5</v>
+      </c>
+      <c r="L35">
+        <v>5</v>
+      </c>
+      <c r="M35">
+        <v>4</v>
+      </c>
+      <c r="N35">
+        <v>4</v>
+      </c>
+      <c r="O35">
+        <v>3</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
@@ -1442,6 +1964,24 @@
       <c r="I36" t="str">
         <v>C</v>
       </c>
+      <c r="J36">
+        <v>5</v>
+      </c>
+      <c r="K36">
+        <v>3</v>
+      </c>
+      <c r="L36">
+        <v>4</v>
+      </c>
+      <c r="M36">
+        <v>5</v>
+      </c>
+      <c r="N36">
+        <v>5</v>
+      </c>
+      <c r="O36">
+        <v>5</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
@@ -1471,6 +2011,24 @@
       <c r="I37" t="str">
         <v>B</v>
       </c>
+      <c r="J37">
+        <v>4</v>
+      </c>
+      <c r="K37">
+        <v>3</v>
+      </c>
+      <c r="L37">
+        <v>4</v>
+      </c>
+      <c r="M37">
+        <v>3</v>
+      </c>
+      <c r="N37">
+        <v>5</v>
+      </c>
+      <c r="O37">
+        <v>4</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
@@ -1500,6 +2058,24 @@
       <c r="I38" t="str">
         <v>B</v>
       </c>
+      <c r="J38">
+        <v>5</v>
+      </c>
+      <c r="K38">
+        <v>4</v>
+      </c>
+      <c r="L38">
+        <v>4</v>
+      </c>
+      <c r="M38">
+        <v>3</v>
+      </c>
+      <c r="N38">
+        <v>3</v>
+      </c>
+      <c r="O38">
+        <v>1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
@@ -1529,6 +2105,24 @@
       <c r="I39" t="str">
         <v>B</v>
       </c>
+      <c r="J39">
+        <v>1</v>
+      </c>
+      <c r="K39">
+        <v>4</v>
+      </c>
+      <c r="L39">
+        <v>3</v>
+      </c>
+      <c r="M39">
+        <v>3</v>
+      </c>
+      <c r="N39">
+        <v>5</v>
+      </c>
+      <c r="O39">
+        <v>1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
@@ -1558,6 +2152,24 @@
       <c r="I40" t="str">
         <v>B</v>
       </c>
+      <c r="J40">
+        <v>2</v>
+      </c>
+      <c r="K40">
+        <v>4</v>
+      </c>
+      <c r="L40">
+        <v>5</v>
+      </c>
+      <c r="M40">
+        <v>3</v>
+      </c>
+      <c r="N40">
+        <v>3</v>
+      </c>
+      <c r="O40">
+        <v>3</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
@@ -1587,6 +2199,24 @@
       <c r="I41" t="str">
         <v>B</v>
       </c>
+      <c r="J41">
+        <v>5</v>
+      </c>
+      <c r="K41">
+        <v>4</v>
+      </c>
+      <c r="L41">
+        <v>4</v>
+      </c>
+      <c r="M41">
+        <v>5</v>
+      </c>
+      <c r="N41">
+        <v>4</v>
+      </c>
+      <c r="O41">
+        <v>4</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
@@ -1616,6 +2246,24 @@
       <c r="I42" t="str">
         <v>C</v>
       </c>
+      <c r="J42">
+        <v>3</v>
+      </c>
+      <c r="K42">
+        <v>5</v>
+      </c>
+      <c r="L42">
+        <v>5</v>
+      </c>
+      <c r="M42">
+        <v>1</v>
+      </c>
+      <c r="N42">
+        <v>5</v>
+      </c>
+      <c r="O42">
+        <v>5</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
@@ -1645,6 +2293,24 @@
       <c r="I43" t="str">
         <v>B</v>
       </c>
+      <c r="J43">
+        <v>3</v>
+      </c>
+      <c r="K43">
+        <v>2</v>
+      </c>
+      <c r="L43">
+        <v>4</v>
+      </c>
+      <c r="M43">
+        <v>5</v>
+      </c>
+      <c r="N43">
+        <v>4</v>
+      </c>
+      <c r="O43">
+        <v>1</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
@@ -1674,6 +2340,24 @@
       <c r="I44" t="str">
         <v>C</v>
       </c>
+      <c r="J44">
+        <v>3</v>
+      </c>
+      <c r="K44">
+        <v>4</v>
+      </c>
+      <c r="L44">
+        <v>4</v>
+      </c>
+      <c r="M44">
+        <v>5</v>
+      </c>
+      <c r="N44">
+        <v>5</v>
+      </c>
+      <c r="O44">
+        <v>3</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
@@ -1703,6 +2387,24 @@
       <c r="I45" t="str">
         <v>C</v>
       </c>
+      <c r="J45">
+        <v>4</v>
+      </c>
+      <c r="K45">
+        <v>5</v>
+      </c>
+      <c r="L45">
+        <v>1</v>
+      </c>
+      <c r="M45">
+        <v>5</v>
+      </c>
+      <c r="N45">
+        <v>3</v>
+      </c>
+      <c r="O45">
+        <v>4</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
@@ -1732,6 +2434,24 @@
       <c r="I46" t="str">
         <v>C</v>
       </c>
+      <c r="J46">
+        <v>5</v>
+      </c>
+      <c r="K46">
+        <v>5</v>
+      </c>
+      <c r="L46">
+        <v>2</v>
+      </c>
+      <c r="M46">
+        <v>4</v>
+      </c>
+      <c r="N46">
+        <v>4</v>
+      </c>
+      <c r="O46">
+        <v>4</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
@@ -1761,6 +2481,24 @@
       <c r="I47" t="str">
         <v>D</v>
       </c>
+      <c r="J47">
+        <v>5</v>
+      </c>
+      <c r="K47">
+        <v>2</v>
+      </c>
+      <c r="L47">
+        <v>4</v>
+      </c>
+      <c r="M47">
+        <v>5</v>
+      </c>
+      <c r="N47">
+        <v>5</v>
+      </c>
+      <c r="O47">
+        <v>2</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
@@ -1790,6 +2528,24 @@
       <c r="I48" t="str">
         <v>B</v>
       </c>
+      <c r="J48">
+        <v>2</v>
+      </c>
+      <c r="K48">
+        <v>5</v>
+      </c>
+      <c r="L48">
+        <v>4</v>
+      </c>
+      <c r="M48">
+        <v>5</v>
+      </c>
+      <c r="N48">
+        <v>5</v>
+      </c>
+      <c r="O48">
+        <v>2</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
@@ -1819,6 +2575,24 @@
       <c r="I49" t="str">
         <v>B</v>
       </c>
+      <c r="J49">
+        <v>4</v>
+      </c>
+      <c r="K49">
+        <v>1</v>
+      </c>
+      <c r="L49">
+        <v>5</v>
+      </c>
+      <c r="M49">
+        <v>3</v>
+      </c>
+      <c r="N49">
+        <v>4</v>
+      </c>
+      <c r="O49">
+        <v>3</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
@@ -1848,6 +2622,24 @@
       <c r="I50" t="str">
         <v>B</v>
       </c>
+      <c r="J50">
+        <v>3</v>
+      </c>
+      <c r="K50">
+        <v>4</v>
+      </c>
+      <c r="L50">
+        <v>3</v>
+      </c>
+      <c r="M50">
+        <v>4</v>
+      </c>
+      <c r="N50">
+        <v>3</v>
+      </c>
+      <c r="O50">
+        <v>1</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
@@ -1877,6 +2669,24 @@
       <c r="I51" t="str">
         <v>B</v>
       </c>
+      <c r="J51">
+        <v>5</v>
+      </c>
+      <c r="K51">
+        <v>5</v>
+      </c>
+      <c r="L51">
+        <v>5</v>
+      </c>
+      <c r="M51">
+        <v>2</v>
+      </c>
+      <c r="N51">
+        <v>2</v>
+      </c>
+      <c r="O51">
+        <v>2</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
@@ -1906,6 +2716,24 @@
       <c r="I52" t="str">
         <v>A</v>
       </c>
+      <c r="J52">
+        <v>5</v>
+      </c>
+      <c r="K52">
+        <v>4</v>
+      </c>
+      <c r="L52">
+        <v>4</v>
+      </c>
+      <c r="M52">
+        <v>5</v>
+      </c>
+      <c r="N52">
+        <v>2</v>
+      </c>
+      <c r="O52">
+        <v>2</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
@@ -1935,6 +2763,24 @@
       <c r="I53" t="str">
         <v>B</v>
       </c>
+      <c r="J53">
+        <v>2</v>
+      </c>
+      <c r="K53">
+        <v>4</v>
+      </c>
+      <c r="L53">
+        <v>5</v>
+      </c>
+      <c r="M53">
+        <v>5</v>
+      </c>
+      <c r="N53">
+        <v>3</v>
+      </c>
+      <c r="O53">
+        <v>4</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
@@ -1964,6 +2810,24 @@
       <c r="I54" t="str">
         <v>C</v>
       </c>
+      <c r="J54">
+        <v>5</v>
+      </c>
+      <c r="K54">
+        <v>4</v>
+      </c>
+      <c r="L54">
+        <v>4</v>
+      </c>
+      <c r="M54">
+        <v>4</v>
+      </c>
+      <c r="N54">
+        <v>3</v>
+      </c>
+      <c r="O54">
+        <v>5</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
@@ -1993,6 +2857,24 @@
       <c r="I55" t="str">
         <v>A</v>
       </c>
+      <c r="J55">
+        <v>4</v>
+      </c>
+      <c r="K55">
+        <v>5</v>
+      </c>
+      <c r="L55">
+        <v>4</v>
+      </c>
+      <c r="M55">
+        <v>5</v>
+      </c>
+      <c r="N55">
+        <v>2</v>
+      </c>
+      <c r="O55">
+        <v>2</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
@@ -2022,6 +2904,24 @@
       <c r="I56" t="str">
         <v>C</v>
       </c>
+      <c r="J56">
+        <v>3</v>
+      </c>
+      <c r="K56">
+        <v>2</v>
+      </c>
+      <c r="L56">
+        <v>1</v>
+      </c>
+      <c r="M56">
+        <v>4</v>
+      </c>
+      <c r="N56">
+        <v>1</v>
+      </c>
+      <c r="O56">
+        <v>5</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
@@ -2051,6 +2951,24 @@
       <c r="I57" t="str">
         <v>C</v>
       </c>
+      <c r="J57">
+        <v>4</v>
+      </c>
+      <c r="K57">
+        <v>3</v>
+      </c>
+      <c r="L57">
+        <v>4</v>
+      </c>
+      <c r="M57">
+        <v>4</v>
+      </c>
+      <c r="N57">
+        <v>1</v>
+      </c>
+      <c r="O57">
+        <v>4</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
@@ -2080,6 +2998,24 @@
       <c r="I58" t="str">
         <v>B</v>
       </c>
+      <c r="J58">
+        <v>4</v>
+      </c>
+      <c r="K58">
+        <v>5</v>
+      </c>
+      <c r="L58">
+        <v>2</v>
+      </c>
+      <c r="M58">
+        <v>1</v>
+      </c>
+      <c r="N58">
+        <v>5</v>
+      </c>
+      <c r="O58">
+        <v>5</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
@@ -2109,6 +3045,24 @@
       <c r="I59" t="str">
         <v>D</v>
       </c>
+      <c r="J59">
+        <v>1</v>
+      </c>
+      <c r="K59">
+        <v>3</v>
+      </c>
+      <c r="L59">
+        <v>2</v>
+      </c>
+      <c r="M59">
+        <v>3</v>
+      </c>
+      <c r="N59">
+        <v>5</v>
+      </c>
+      <c r="O59">
+        <v>4</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
@@ -2138,6 +3092,24 @@
       <c r="I60" t="str">
         <v>B</v>
       </c>
+      <c r="J60">
+        <v>1</v>
+      </c>
+      <c r="K60">
+        <v>5</v>
+      </c>
+      <c r="L60">
+        <v>1</v>
+      </c>
+      <c r="M60">
+        <v>3</v>
+      </c>
+      <c r="N60">
+        <v>3</v>
+      </c>
+      <c r="O60">
+        <v>2</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
@@ -2167,6 +3139,24 @@
       <c r="I61" t="str">
         <v>B</v>
       </c>
+      <c r="J61">
+        <v>4</v>
+      </c>
+      <c r="K61">
+        <v>4</v>
+      </c>
+      <c r="L61">
+        <v>5</v>
+      </c>
+      <c r="M61">
+        <v>1</v>
+      </c>
+      <c r="N61">
+        <v>3</v>
+      </c>
+      <c r="O61">
+        <v>1</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
@@ -2196,6 +3186,24 @@
       <c r="I62" t="str">
         <v>B</v>
       </c>
+      <c r="J62">
+        <v>4</v>
+      </c>
+      <c r="K62">
+        <v>5</v>
+      </c>
+      <c r="L62">
+        <v>4</v>
+      </c>
+      <c r="M62">
+        <v>5</v>
+      </c>
+      <c r="N62">
+        <v>3</v>
+      </c>
+      <c r="O62">
+        <v>1</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
@@ -2225,6 +3233,24 @@
       <c r="I63" t="str">
         <v>B</v>
       </c>
+      <c r="J63">
+        <v>5</v>
+      </c>
+      <c r="K63">
+        <v>3</v>
+      </c>
+      <c r="L63">
+        <v>3</v>
+      </c>
+      <c r="M63">
+        <v>2</v>
+      </c>
+      <c r="N63">
+        <v>3</v>
+      </c>
+      <c r="O63">
+        <v>1</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
@@ -2254,6 +3280,24 @@
       <c r="I64" t="str">
         <v>B</v>
       </c>
+      <c r="J64">
+        <v>3</v>
+      </c>
+      <c r="K64">
+        <v>4</v>
+      </c>
+      <c r="L64">
+        <v>5</v>
+      </c>
+      <c r="M64">
+        <v>4</v>
+      </c>
+      <c r="N64">
+        <v>3</v>
+      </c>
+      <c r="O64">
+        <v>4</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
@@ -2283,6 +3327,24 @@
       <c r="I65" t="str">
         <v>B</v>
       </c>
+      <c r="J65">
+        <v>3</v>
+      </c>
+      <c r="K65">
+        <v>1</v>
+      </c>
+      <c r="L65">
+        <v>5</v>
+      </c>
+      <c r="M65">
+        <v>1</v>
+      </c>
+      <c r="N65">
+        <v>2</v>
+      </c>
+      <c r="O65">
+        <v>5</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
@@ -2312,6 +3374,24 @@
       <c r="I66" t="str">
         <v>A</v>
       </c>
+      <c r="J66">
+        <v>4</v>
+      </c>
+      <c r="K66">
+        <v>3</v>
+      </c>
+      <c r="L66">
+        <v>4</v>
+      </c>
+      <c r="M66">
+        <v>4</v>
+      </c>
+      <c r="N66">
+        <v>5</v>
+      </c>
+      <c r="O66">
+        <v>5</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
@@ -2341,6 +3421,24 @@
       <c r="I67" t="str">
         <v>D</v>
       </c>
+      <c r="J67">
+        <v>3</v>
+      </c>
+      <c r="K67">
+        <v>2</v>
+      </c>
+      <c r="L67">
+        <v>3</v>
+      </c>
+      <c r="M67">
+        <v>3</v>
+      </c>
+      <c r="N67">
+        <v>5</v>
+      </c>
+      <c r="O67">
+        <v>3</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
@@ -2370,10 +3468,28 @@
       <c r="I68" t="str">
         <v>A</v>
       </c>
+      <c r="J68">
+        <v>3</v>
+      </c>
+      <c r="K68">
+        <v>4</v>
+      </c>
+      <c r="L68">
+        <v>5</v>
+      </c>
+      <c r="M68">
+        <v>4</v>
+      </c>
+      <c r="N68">
+        <v>5</v>
+      </c>
+      <c r="O68">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I68"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O68"/>
   </ignoredErrors>
 </worksheet>
 </file>